--- a/final_score.xlsx
+++ b/final_score.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009B2727-0750-429A-AE2B-DBA25CCE61C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB03D8F-2451-4C1D-9D75-1106578CDCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="myCPU计算" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">myCPU计算!$B$7:$G$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -214,509 +214,507 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上板</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>进制</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>CPU频率（MHz）</t>
+  </si>
+  <si>
+    <t>数码管显示
+(CPU count)
+(最左开关拨下)</t>
+  </si>
+  <si>
+    <t>数码管显示
+(SoC count)
+(最左开关拨上)</t>
+  </si>
+  <si>
+    <t>cpu_clk : sys_clk</t>
+  </si>
+  <si>
+    <t>xxMHz : 100MHz</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>33MHz : 100MHz</t>
+  </si>
+  <si>
+    <t>bitcount</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>00053e76</t>
+  </si>
+  <si>
+    <t>bubble_sort</t>
+  </si>
+  <si>
+    <t>001866a1</t>
+  </si>
+  <si>
+    <t>coremark</t>
+  </si>
+  <si>
+    <t>003ef0a9</t>
+  </si>
+  <si>
+    <t>crc32</t>
+  </si>
+  <si>
+    <t>00276e3a</t>
+  </si>
+  <si>
+    <t>dhrystone</t>
+  </si>
+  <si>
+    <t>0000b682</t>
+  </si>
+  <si>
+    <t>quick_sort</t>
+  </si>
+  <si>
+    <t>001e1118</t>
+  </si>
+  <si>
+    <t>select_sort</t>
+  </si>
+  <si>
+    <t>000fe246</t>
+  </si>
+  <si>
+    <t>sha</t>
+  </si>
+  <si>
+    <t>00216663</t>
+  </si>
+  <si>
+    <t>stream_copy</t>
+  </si>
+  <si>
+    <t>0001fb56</t>
+  </si>
+  <si>
+    <t>stringsearch</t>
+  </si>
+  <si>
+    <t>000761f2</t>
+  </si>
+  <si>
+    <t>fireye_A0</t>
+  </si>
+  <si>
+    <t>0040c307</t>
+  </si>
+  <si>
+    <t>fireye_B2</t>
+  </si>
+  <si>
+    <t>00084dc7</t>
+  </si>
+  <si>
+    <t>fireye_C0</t>
+  </si>
+  <si>
+    <t>000a4ca1</t>
+  </si>
+  <si>
+    <t>fireye_D1</t>
+  </si>
+  <si>
+    <t>005bd70d</t>
+  </si>
+  <si>
+    <t>fireye_I2</t>
+  </si>
+  <si>
+    <t>003b9ba0</t>
+  </si>
+  <si>
+    <t>inner_product</t>
+  </si>
+  <si>
+    <t>00f7dcb6</t>
+  </si>
+  <si>
+    <t>lookup_table</t>
+  </si>
+  <si>
+    <t>002d2e61</t>
+  </si>
+  <si>
+    <t>loop_induction</t>
+  </si>
+  <si>
+    <t>00a90cc0</t>
+  </si>
+  <si>
+    <t>my_memcmp</t>
+  </si>
+  <si>
+    <t>0033db02</t>
+  </si>
+  <si>
+    <t>minmax_sequence</t>
+  </si>
+  <si>
+    <t>003c262e</t>
+  </si>
+  <si>
+    <t>三、系统测试分数计算</t>
+  </si>
+  <si>
+    <t>完成系统测试点</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>完成状态序号（只选完成的最大序号，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>左侧红色标识</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、未成功启动任一项</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、成功启动典型 bootloader（如 U-Boot、PMON）并完成指定功能操作</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、成功启动典型教学操作系统（如 ucore）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、成功启动 Linux 操作系统</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、成功启动 Linux 操作系统，并成功运行"ls"命令</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>注1：根据myCPU运行时间填写黄色区域，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不要更改单元格格式，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>填写格式为16进制数，分别填写：上板cpu_clk与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_clk的频率，上板计时；</t>
+    </r>
+  </si>
+  <si>
+    <t>注2：表格中计时结果为上板时性能测试通过时的数码管显示。</t>
+  </si>
+  <si>
+    <t>注3：如果某性能测试程序不通过，则对应仿真计时和上板计时项填为0，此时该项与openla500比值按0.1算，最终预赛评分时可能会调整；</t>
+  </si>
+  <si>
+    <t>注4：灰色部分为固定项，不可修改；</t>
+  </si>
+  <si>
+    <t>注5：橙色部分为自动计算，不可修改；</t>
+  </si>
+  <si>
+    <t>注6：红色部分自动计算性能得分。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">CPU count </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>: SoC count
+（≈cpu_clk : sys_clk）</t>
+    </r>
+  </si>
+  <si>
+    <t>数码管显示(CPU count)</t>
+  </si>
+  <si>
+    <t>数码管显示(SoC count)</t>
+  </si>
+  <si>
+    <t>00100b31</t>
+  </si>
+  <si>
+    <t>004a9668</t>
+  </si>
+  <si>
+    <t>00c05e33</t>
+  </si>
+  <si>
+    <t>0078d187</t>
+  </si>
+  <si>
+    <t>000235bb</t>
+  </si>
+  <si>
+    <t>005bead9</t>
+  </si>
+  <si>
+    <t>00308ea1</t>
+  </si>
+  <si>
+    <t>006674f5</t>
+  </si>
+  <si>
+    <t>000616a5</t>
+  </si>
+  <si>
+    <t>001d2837</t>
+  </si>
+  <si>
+    <t>00c5ea69</t>
+  </si>
+  <si>
+    <t>0019658a</t>
+  </si>
+  <si>
+    <t>001f7fc5</t>
+  </si>
+  <si>
+    <t>0118a87a</t>
+  </si>
+  <si>
+    <t>00b62beb</t>
+  </si>
+  <si>
+    <t>02f5639a</t>
+  </si>
+  <si>
+    <t>008a1b9b</t>
+  </si>
+  <si>
+    <t>0204956c</t>
+  </si>
+  <si>
+    <t>009e7b95</t>
+  </si>
+  <si>
+    <t>00b7d4db</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPU count
  : SoC cout
 </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>上板</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(16</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进制</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>CPU频率（MHz）</t>
-  </si>
-  <si>
-    <t>数码管显示
-(CPU count)
-(最左开关拨下)</t>
-  </si>
-  <si>
-    <t>数码管显示
-(SoC count)
-(最左开关拨上)</t>
-  </si>
-  <si>
-    <t>cpu_clk : sys_clk</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>bitcount</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>bubble_sort</t>
-  </si>
-  <si>
-    <t>coremark</t>
-  </si>
-  <si>
-    <t>crc32</t>
-  </si>
-  <si>
-    <t>dhrystone</t>
-  </si>
-  <si>
-    <t>quick_sort</t>
-  </si>
-  <si>
-    <t>select_sort</t>
-  </si>
-  <si>
-    <t>sha</t>
-  </si>
-  <si>
-    <t>stream_copy</t>
-  </si>
-  <si>
-    <t>stringsearch</t>
-  </si>
-  <si>
-    <t>fireye_A0</t>
-  </si>
-  <si>
-    <t>fireye_B2</t>
-  </si>
-  <si>
-    <t>fireye_C0</t>
-  </si>
-  <si>
-    <t>fireye_D1</t>
-  </si>
-  <si>
-    <t>fireye_I2</t>
-  </si>
-  <si>
-    <t>inner_product</t>
-  </si>
-  <si>
-    <t>lookup_table</t>
-  </si>
-  <si>
-    <t>loop_induction</t>
-  </si>
-  <si>
-    <t>my_memcmp</t>
-  </si>
-  <si>
-    <t>minmax_sequence</t>
-  </si>
-  <si>
-    <t>三、系统测试分数计算</t>
-  </si>
-  <si>
-    <t>完成系统测试点</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>完成状态序号（只选完成的最大序号，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>左侧红色标识</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、未成功启动任一项</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、成功启动典型 bootloader（如 U-Boot、PMON）并完成指定功能操作</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、成功启动典型教学操作系统（如 ucore）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、成功启动 Linux 操作系统</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>、成功启动 Linux 操作系统，并成功运行"ls"命令</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>注1：根据myCPU运行时间填写黄色区域，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>不要更改单元格格式，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>填写格式为16进制数，分别填写：上板cpu_clk与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>sys</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_clk的频率，上板计时；</t>
-    </r>
-  </si>
-  <si>
-    <t>注2：表格中计时结果为上板时性能测试通过时的数码管显示。</t>
-  </si>
-  <si>
-    <t>注3：如果某性能测试程序不通过，则对应仿真计时和上板计时项填为0，此时该项与openla500比值按0.1算，最终预赛评分时可能会调整；</t>
-  </si>
-  <si>
-    <t>注4：灰色部分为固定项，不可修改；</t>
-  </si>
-  <si>
-    <t>注5：橙色部分为自动计算，不可修改；</t>
-  </si>
-  <si>
-    <t>注6：红色部分自动计算性能得分。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">CPU count </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>: SoC count
-（≈cpu_clk : sys_clk）</t>
-    </r>
-  </si>
-  <si>
-    <t>数码管显示(CPU count)</t>
-  </si>
-  <si>
-    <t>数码管显示(SoC count)</t>
-  </si>
-  <si>
-    <t>33MHz : 100MHz</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>00100b31</t>
-  </si>
-  <si>
-    <t>004a9668</t>
-  </si>
-  <si>
-    <t>00c05e33</t>
-  </si>
-  <si>
-    <t>0078d187</t>
-  </si>
-  <si>
-    <t>000235bb</t>
-  </si>
-  <si>
-    <t>005bead9</t>
-  </si>
-  <si>
-    <t>00308ea1</t>
-  </si>
-  <si>
-    <t>006674f5</t>
-  </si>
-  <si>
-    <t>000616a5</t>
-  </si>
-  <si>
-    <t>001d2837</t>
-  </si>
-  <si>
-    <t>00c5ea69</t>
-  </si>
-  <si>
-    <t>001f7fc5</t>
-  </si>
-  <si>
-    <t>0118a87a</t>
-  </si>
-  <si>
-    <t>00b62beb</t>
-  </si>
-  <si>
-    <t>02f5639a</t>
-  </si>
-  <si>
-    <t>008a1b9b</t>
-  </si>
-  <si>
-    <t>0204956c</t>
-  </si>
-  <si>
-    <t>009e7b95</t>
-  </si>
-  <si>
-    <t>00b7d4db</t>
-  </si>
-  <si>
-    <t>00053e76</t>
-  </si>
-  <si>
-    <t>001866a1</t>
-  </si>
-  <si>
-    <t>003ef0a9</t>
-  </si>
-  <si>
-    <t>00276e3a</t>
-  </si>
-  <si>
-    <t>0000b682</t>
-  </si>
-  <si>
-    <t>001e1118</t>
-  </si>
-  <si>
-    <t>000fe246</t>
-  </si>
-  <si>
-    <t>00216663</t>
-  </si>
-  <si>
-    <t>0001fb56</t>
-  </si>
-  <si>
-    <t>000761f2</t>
-  </si>
-  <si>
-    <t>0040c307</t>
-  </si>
-  <si>
-    <t>00084dc7</t>
-  </si>
-  <si>
-    <t>000a4ca1</t>
-  </si>
-  <si>
-    <t>005bd70d</t>
-  </si>
-  <si>
-    <t>003b9ba0</t>
-  </si>
-  <si>
-    <t>00f7dcb6</t>
-  </si>
-  <si>
-    <t>002d2e61</t>
-  </si>
-  <si>
-    <t>00a90cc0</t>
-  </si>
-  <si>
-    <t>0033db02</t>
-  </si>
-  <si>
-    <t>003c262e</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>xxMHz : 100MHz</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>0019658a</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -725,10 +723,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="179" formatCode="0_ "/>
-    <numFmt numFmtId="180" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -827,12 +825,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <vertAlign val="subscript"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -840,12 +832,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -859,6 +849,20 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -877,13 +881,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
+        <fgColor theme="0" tint="-0.14990691854609822"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +899,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <fgColor theme="0" tint="-0.14993743705557422"/>
         <bgColor theme="1"/>
       </patternFill>
     </fill>
@@ -907,7 +911,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14993743705557422"/>
+        <fgColor theme="0" tint="-0.14990691854609822"/>
         <bgColor theme="1"/>
       </patternFill>
     </fill>
@@ -919,7 +923,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.14996795556505021"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1064,6 +1068,9 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1085,7 +1092,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1117,8 +1124,12 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1197,17 +1208,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1513,871 +1518,872 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:N55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.77734375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="27" style="7" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" style="7" customWidth="1"/>
-    <col min="9" max="9" width="3.109375" style="7" customWidth="1"/>
-    <col min="10" max="10" width="20.5546875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="7" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="5.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" customWidth="1"/>
+    <col min="3" max="3" width="18.75" style="8" customWidth="1"/>
+    <col min="4" max="4" width="35.625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="27" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.75" style="8" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="8" customWidth="1"/>
+    <col min="8" max="8" width="18.375" style="8" customWidth="1"/>
+    <col min="9" max="9" width="3.125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="20.5" style="8" customWidth="1"/>
+    <col min="11" max="11" width="16.625" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="1:14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="8" t="s">
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="25"/>
-    </row>
-    <row r="3" spans="1:11" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8" t="s">
+      <c r="F2" s="28"/>
+      <c r="G2" s="27"/>
+    </row>
+    <row r="3" spans="1:14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
-    </row>
-    <row r="4" spans="1:11" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" s="6" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="F3" s="26"/>
+      <c r="G3" s="27"/>
+    </row>
+    <row r="4" spans="1:14" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="8"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" s="7" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11" t="s">
+    <row r="7" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J14" s="21" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J14" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="23">
         <f>C8/58*100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="6" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:14" s="7" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-    </row>
-    <row r="17" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="37" t="s">
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="N16" s="24"/>
+    </row>
+    <row r="17" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="14" t="s">
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="22">
-        <f>GEOMEAN(H21:H30)</f>
+      <c r="K17" s="23">
+        <f>GEOMEAN(H21:H40)</f>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="32" t="s">
+    <row r="18" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="42" t="s">
+      <c r="E18" s="35"/>
+      <c r="F18" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="H18" s="46"/>
+      <c r="J18" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="44"/>
-      <c r="J18" s="21" t="s">
+      <c r="K18" s="25"/>
+    </row>
+    <row r="19" spans="2:11" ht="48.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="23"/>
-    </row>
-    <row r="19" spans="2:11" ht="48.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="46"/>
+    </row>
+    <row r="20" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="44"/>
-    </row>
-    <row r="20" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="34" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="36"/>
+      <c r="E20" s="38"/>
       <c r="F20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="17" t="s">
+      <c r="G20" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="15">
+    <row r="21" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="16">
         <v>1</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>106</v>
+      <c r="C21" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F21" s="4">
         <f>IF(HEX2DEC(D21),HEX2DEC(D21)/HEX2DEC(E21),0)</f>
         <v>0</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="19">
+        <v>31</v>
+      </c>
+      <c r="H21" s="20">
         <f>IF(HEX2DEC(D21),HEX2DEC(G21)/HEX2DEC(D21),0.0001)</f>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="15">
+    <row r="22" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="16">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>29</v>
+      <c r="C22" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F22" s="4">
         <f t="shared" ref="F22:F30" si="0">IF(HEX2DEC(D22),HEX2DEC(D22)/HEX2DEC(E22),0)</f>
         <v>0</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="19">
+        <v>33</v>
+      </c>
+      <c r="H22" s="20">
         <f t="shared" ref="H22:H40" si="1">IF(HEX2DEC(D22),HEX2DEC(G22)/HEX2DEC(D22),0.0001)</f>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="15">
+    <row r="23" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="16">
         <v>3</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>29</v>
+      <c r="C23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F23" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="19">
+        <v>35</v>
+      </c>
+      <c r="H23" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="15">
+    <row r="24" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="16">
         <v>4</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>29</v>
+      <c r="C24" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F24" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="19">
+        <v>37</v>
+      </c>
+      <c r="H24" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="15">
+    <row r="25" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="16">
         <v>5</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>29</v>
+      <c r="C25" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F25" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="19">
+        <v>39</v>
+      </c>
+      <c r="H25" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="15">
+    <row r="26" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="16">
         <v>6</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>29</v>
+      <c r="C26" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="F26" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="H26" s="19">
+        <v>41</v>
+      </c>
+      <c r="H26" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="15">
+    <row r="27" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="16">
         <v>7</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>29</v>
+      <c r="C27" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F27" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="19">
+        <v>43</v>
+      </c>
+      <c r="H27" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="15">
+    <row r="28" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="16">
         <v>8</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>29</v>
+      <c r="C28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F28" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="19">
+        <v>45</v>
+      </c>
+      <c r="H28" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="15">
+    <row r="29" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="16">
         <v>9</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>29</v>
+      <c r="C29" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F29" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" s="19">
+        <v>47</v>
+      </c>
+      <c r="H29" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="30" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="15">
+    <row r="30" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="16">
         <v>10</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>29</v>
+      <c r="C30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H30" s="19">
+        <v>49</v>
+      </c>
+      <c r="H30" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="15">
+    <row r="31" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="16">
         <v>11</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>29</v>
+        <v>50</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" ref="F31:F40" si="2">IF(HEX2DEC(D31),HEX2DEC(D31)/HEX2DEC(E31),0)</f>
         <v>0</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H31" s="19">
+        <v>51</v>
+      </c>
+      <c r="H31" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="15">
+    <row r="32" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="16">
         <v>12</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>29</v>
+        <v>52</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F32" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H32" s="19">
+        <v>53</v>
+      </c>
+      <c r="H32" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="15">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="16">
         <v>13</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>29</v>
+        <v>54</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F33" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H33" s="19">
+        <v>55</v>
+      </c>
+      <c r="H33" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="15">
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="16">
         <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>29</v>
+        <v>56</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F34" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H34" s="19">
+        <v>57</v>
+      </c>
+      <c r="H34" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="15">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="16">
         <v>15</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>29</v>
+        <v>58</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="19">
+        <v>59</v>
+      </c>
+      <c r="H35" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="15">
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="16">
         <v>16</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>29</v>
+        <v>60</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F36" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H36" s="19">
+        <v>61</v>
+      </c>
+      <c r="H36" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="15">
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="16">
         <v>17</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>29</v>
+        <v>62</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F37" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H37" s="19">
+        <v>63</v>
+      </c>
+      <c r="H37" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="15">
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="16">
         <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>29</v>
+        <v>64</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H38" s="19">
+        <v>65</v>
+      </c>
+      <c r="H38" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="15">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="16">
         <v>19</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>29</v>
+        <v>66</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F39" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="19">
+        <v>67</v>
+      </c>
+      <c r="H39" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="15">
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="16">
         <v>20</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>106</v>
+        <v>68</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="F40" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" s="19">
+        <v>69</v>
+      </c>
+      <c r="H40" s="20">
         <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-    </row>
-    <row r="44" spans="1:8" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F44" s="39"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-    </row>
-    <row r="45" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="45">
+    <row r="42" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" s="41"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="47">
         <v>0</v>
       </c>
-      <c r="F45" s="45"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-    </row>
-    <row r="46" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="41"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-    </row>
-    <row r="54" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-    </row>
-    <row r="55" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+    </row>
+    <row r="46" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B46" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+    </row>
+    <row r="48" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+    </row>
+    <row r="49" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+    </row>
+    <row r="50" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+    </row>
+    <row r="52" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+    </row>
+    <row r="53" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+    </row>
+    <row r="54" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+    </row>
+    <row r="55" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="i9dXIAvDmkyhR0fit0aluntT4GgQ2lJMetpRV0YIkIA+GSKPIemS03iUkG4Pc8FpX/3qGwr5zD1vKqnevGzLog==" saltValue="FzGs5gN4O8kyef5WPJPfjg==" spinCount="100000" sheet="1" objects="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="FokfN492+i32Q0c0M+zU/rcGkAYZppr/YIwmZbAbQOBzrp0FAtbF/29bJnVqK5VH+7P8nyzAaUh6jZGSEnlm6A==" saltValue="UU3jYivebWaINDxCsowpPw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="F2:G3 C2:D3 C8 D20:E40 E45 K18" name="允许修改"/>
+    <protectedRange sqref="F2:G3 C2:D3 C8 D20:E40 E45 K18" name="允许修改" securityDescriptor="O:WDG:WDD:"/>
   </protectedRanges>
   <mergeCells count="21">
     <mergeCell ref="H17:H19"/>
@@ -2412,8 +2418,8 @@
       <formula1>0</formula1>
       <formula2>89</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="上板频率" prompt="格式为:XX MHz : 100MHz_x000a_XX MHz为myCPU上板频率，timer_clk必须为100MHz" sqref="D20 E20 F20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="输入计时结果" prompt="要求为16进制数。_x000a_如结果为0x144FF46，则填写144FF46。_x000a_如果某一性能测试未通过，则填写0" sqref="D21:D40 E21:E40" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="上板频率" prompt="格式为:XX MHz : 100MHz_x000a_XX MHz为myCPU上板频率，timer_clk必须为100MHz" sqref="D20:F20" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="输入计时结果" prompt="要求为16进制数。_x000a_如结果为0x144FF46，则填写144FF46。_x000a_如果某一性能测试未通过，则填写0" sqref="D21:E40" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E45:F49" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>0</formula1>
       <formula2>4</formula2>
@@ -2427,416 +2433,415 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="51"/>
+    <col min="1" max="1" width="9.125" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="22.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="49" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
+        <v>21</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="49"/>
-    </row>
-    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="46"/>
+        <v>86</v>
+      </c>
+      <c r="E2" s="51"/>
+    </row>
+    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="48"/>
       <c r="C3" s="4" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3">
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="50">
+        <v>87</v>
+      </c>
+      <c r="E4" s="5">
         <f>IF(HEX2DEC(C4),HEX2DEC(C4)/HEX2DEC(D4),0)</f>
         <v>0.32685619069448502</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="50">
+        <v>88</v>
+      </c>
+      <c r="E5" s="5">
         <f t="shared" ref="E5:E23" si="0">IF(HEX2DEC(C5),HEX2DEC(C5)/HEX2DEC(D5),0)</f>
-        <v>0.32714444348066596</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32714444348066601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="50">
+        <v>89</v>
+      </c>
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
-        <v>0.32718586229727276</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32718586229727298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="50">
+        <v>90</v>
+      </c>
+      <c r="E7" s="5">
         <f t="shared" si="0"/>
-        <v>0.32636213448440438</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32636213448440399</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3">
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="50">
+        <v>91</v>
+      </c>
+      <c r="E8" s="5">
         <f t="shared" si="0"/>
-        <v>0.32260559149882273</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32260559149882301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3">
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="50">
+        <v>92</v>
+      </c>
+      <c r="E9" s="5">
         <f t="shared" si="0"/>
-        <v>0.3271065225716841</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32710652257168399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3">
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" s="50">
+        <v>93</v>
+      </c>
+      <c r="E10" s="5">
         <f t="shared" si="0"/>
-        <v>0.32711727364457938</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32711727364457899</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3">
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="50">
+        <v>94</v>
+      </c>
+      <c r="E11" s="5">
         <f t="shared" si="0"/>
-        <v>0.32599034374728669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32599034374728703</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="50">
+        <v>95</v>
+      </c>
+      <c r="E12" s="5">
         <f t="shared" si="0"/>
-        <v>0.32549816672639736</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0.32549816672639698</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="50">
+        <v>96</v>
+      </c>
+      <c r="E13" s="5">
         <f t="shared" si="0"/>
-        <v>0.25320081911662889</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+        <v>0.25320081911662901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="50">
+        <v>97</v>
+      </c>
+      <c r="E14" s="5">
         <f t="shared" si="0"/>
-        <v>0.32721930155742207</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+        <v>0.32721930155742202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="6">
         <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="50">
+        <v>98</v>
+      </c>
+      <c r="E15" s="5">
         <f t="shared" si="0"/>
-        <v>0.32696524981464725</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+        <v>0.32696524981464697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="6">
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="50">
+        <v>99</v>
+      </c>
+      <c r="E16" s="5">
         <f t="shared" si="0"/>
-        <v>0.32697225485328135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+        <v>0.32697225485328102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="6">
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="50">
+        <v>100</v>
+      </c>
+      <c r="E17" s="5">
         <f t="shared" si="0"/>
         <v>0.32723102710184898</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+    <row r="18" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="6">
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="50">
+        <v>101</v>
+      </c>
+      <c r="E18" s="5">
         <f t="shared" si="0"/>
-        <v>0.32720756156714309</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+        <v>0.32720756156714298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="6">
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="50">
+        <v>102</v>
+      </c>
+      <c r="E19" s="5">
         <f t="shared" si="0"/>
-        <v>0.3272586869475434</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
+        <v>0.32725868694754301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="6">
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="50">
+        <v>103</v>
+      </c>
+      <c r="E20" s="5">
         <f t="shared" si="0"/>
-        <v>0.32714413324001068</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+        <v>0.32714413324001101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="6">
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="50">
+        <v>104</v>
+      </c>
+      <c r="E21" s="5">
         <f t="shared" si="0"/>
-        <v>0.32724573286858821</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+        <v>0.32724573286858799</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="6">
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="50">
+        <v>105</v>
+      </c>
+      <c r="E22" s="5">
         <f t="shared" si="0"/>
-        <v>0.32719965916722227</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+        <v>0.32719965916722199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="6">
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="50">
+        <v>106</v>
+      </c>
+      <c r="E23" s="5">
         <f t="shared" si="0"/>
-        <v>0.32719719040647088</v>
+        <v>0.32719719040647099</v>
       </c>
     </row>
   </sheetData>
@@ -2847,7 +2852,7 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:E2"/>
   </mergeCells>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -2855,10 +2860,10 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
-  <rangeList sheetStid="1" master="">
+  <rangeList sheetStid="1" master="" otherUserPermission="visible">
     <arrUserId title="允许修改" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
-  <rangeList sheetStid="2" master=""/>
+  <rangeList sheetStid="2" master="" otherUserPermission="visible"/>
 </allowEditUser>
 </file>
 

--- a/final_score.xlsx
+++ b/final_score.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t xml:space="preserve">队名</t>
   </si>
@@ -301,121 +301,61 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">00053E26</t>
-  </si>
-  <si>
     <t xml:space="preserve">bubble_sort</t>
   </si>
   <si>
-    <t xml:space="preserve">00186560</t>
-  </si>
-  <si>
     <t xml:space="preserve">coremark</t>
   </si>
   <si>
-    <t xml:space="preserve">003F1F59</t>
-  </si>
-  <si>
     <t xml:space="preserve">crc32</t>
   </si>
   <si>
-    <t xml:space="preserve">002769F9</t>
-  </si>
-  <si>
     <t xml:space="preserve">dhrystone</t>
   </si>
   <si>
-    <t xml:space="preserve">0000B7A6</t>
-  </si>
-  <si>
     <t xml:space="preserve">quick_sort</t>
   </si>
   <si>
-    <t xml:space="preserve">001E0680</t>
-  </si>
-  <si>
     <t xml:space="preserve">select_sort</t>
   </si>
   <si>
-    <t xml:space="preserve">000FE287</t>
-  </si>
-  <si>
     <t xml:space="preserve">sha</t>
   </si>
   <si>
-    <t xml:space="preserve">00215BBA</t>
-  </si>
-  <si>
     <t xml:space="preserve">stream_copy</t>
   </si>
   <si>
-    <t xml:space="preserve">0001FC67</t>
-  </si>
-  <si>
     <t xml:space="preserve">stringsearch</t>
   </si>
   <si>
-    <t xml:space="preserve">0008E077</t>
-  </si>
-  <si>
     <t xml:space="preserve">fireye_A0</t>
   </si>
   <si>
-    <t xml:space="preserve">0040B822</t>
-  </si>
-  <si>
     <t xml:space="preserve">fireye_B2</t>
   </si>
   <si>
-    <t xml:space="preserve">00084622</t>
-  </si>
-  <si>
     <t xml:space="preserve">fireye_C0</t>
   </si>
   <si>
-    <t xml:space="preserve">000A51E9</t>
-  </si>
-  <si>
     <t xml:space="preserve">fireye_D1</t>
   </si>
   <si>
-    <t xml:space="preserve">005BC44F</t>
-  </si>
-  <si>
     <t xml:space="preserve">fireye_I2</t>
   </si>
   <si>
-    <t xml:space="preserve">003BA045</t>
-  </si>
-  <si>
     <t xml:space="preserve">inner_product</t>
   </si>
   <si>
-    <t xml:space="preserve">00F7A093</t>
-  </si>
-  <si>
     <t xml:space="preserve">lookup_table</t>
   </si>
   <si>
-    <t xml:space="preserve">002D131A</t>
-  </si>
-  <si>
     <t xml:space="preserve">loop_induction</t>
   </si>
   <si>
-    <t xml:space="preserve">00A913D8</t>
-  </si>
-  <si>
     <t xml:space="preserve">my_memcmp</t>
   </si>
   <si>
-    <t xml:space="preserve">0033EE87</t>
-  </si>
-  <si>
     <t xml:space="preserve">minmax_sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003C2869</t>
   </si>
   <si>
     <t xml:space="preserve">三、系统测试分数计算</t>
@@ -635,66 +575,6 @@
   </si>
   <si>
     <t xml:space="preserve">数码管显示(SoC count)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00100A2E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">004A9290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00C0ECF0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0078AE3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0002393D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">005BC618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00309035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0066421B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">000619DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">001B5CCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00C5C934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00194E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">001F8FEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01186F45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00B6389E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02F4ABBE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0089C876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0204A7B9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">009EB58B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00B7DBB2</t>
   </si>
 </sst>
 </file>
@@ -940,35 +820,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -976,19 +856,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -996,23 +876,23 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1020,15 +900,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1036,27 +916,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1069,47 +949,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF66"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1582,8 +1421,8 @@
         <f aca="false">IF(HEX2DEC(D21),HEX2DEC(D21)/HEX2DEC(E21),0)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="21" t="s">
-        <v>32</v>
+      <c r="G21" s="21" t="n">
+        <v>343640</v>
       </c>
       <c r="H21" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D21),HEX2DEC(G21)/HEX2DEC(D21),0.0001)</f>
@@ -1595,7 +1434,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="24" t="s">
         <v>31</v>
@@ -1607,8 +1446,8 @@
         <f aca="false">IF(HEX2DEC(D22),HEX2DEC(D22)/HEX2DEC(E22),0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="21" t="s">
-        <v>34</v>
+      <c r="G22" s="21" t="n">
+        <v>1599254</v>
       </c>
       <c r="H22" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D22),HEX2DEC(G22)/HEX2DEC(D22),0.0001)</f>
@@ -1620,7 +1459,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" s="24" t="s">
         <v>31</v>
@@ -1632,8 +1471,8 @@
         <f aca="false">IF(HEX2DEC(D23),HEX2DEC(D23)/HEX2DEC(E23),0)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="21" t="s">
-        <v>36</v>
+      <c r="G23" s="21" t="n">
+        <v>4130786</v>
       </c>
       <c r="H23" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D23),HEX2DEC(G23)/HEX2DEC(D23),0.0001)</f>
@@ -1645,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D24" s="24" t="s">
         <v>31</v>
@@ -1657,8 +1496,8 @@
         <f aca="false">IF(HEX2DEC(D24),HEX2DEC(D24)/HEX2DEC(E24),0)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="21" t="s">
-        <v>38</v>
+      <c r="G24" s="21" t="n">
+        <v>2583293</v>
       </c>
       <c r="H24" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D24),HEX2DEC(G24)/HEX2DEC(D24),0.0001)</f>
@@ -1670,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D25" s="24" t="s">
         <v>31</v>
@@ -1682,8 +1521,8 @@
         <f aca="false">IF(HEX2DEC(D25),HEX2DEC(D25)/HEX2DEC(E25),0)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="21" t="s">
-        <v>40</v>
+      <c r="G25" s="21" t="n">
+        <v>46601</v>
       </c>
       <c r="H25" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D25),HEX2DEC(G25)/HEX2DEC(D25),0.0001)</f>
@@ -1695,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>31</v>
@@ -1707,8 +1546,8 @@
         <f aca="false">IF(HEX2DEC(D26),HEX2DEC(D26)/HEX2DEC(E26),0)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="21" t="s">
-        <v>42</v>
+      <c r="G26" s="21" t="n">
+        <v>1969534</v>
       </c>
       <c r="H26" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D26),HEX2DEC(G26)/HEX2DEC(D26),0.0001)</f>
@@ -1720,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>31</v>
@@ -1732,8 +1571,8 @@
         <f aca="false">IF(HEX2DEC(D27),HEX2DEC(D27)/HEX2DEC(E27),0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="21" t="s">
-        <v>44</v>
+      <c r="G27" s="21" t="n">
+        <v>1041006</v>
       </c>
       <c r="H27" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D27),HEX2DEC(G27)/HEX2DEC(D27),0.0001)</f>
@@ -1745,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D28" s="24" t="s">
         <v>31</v>
@@ -1757,8 +1596,8 @@
         <f aca="false">IF(HEX2DEC(D28),HEX2DEC(D28)/HEX2DEC(E28),0)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="21" t="s">
-        <v>46</v>
+      <c r="G28" s="21" t="n">
+        <v>2190475</v>
       </c>
       <c r="H28" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D28),HEX2DEC(G28)/HEX2DEC(D28),0.0001)</f>
@@ -1770,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D29" s="24" t="s">
         <v>31</v>
@@ -1782,8 +1621,8 @@
         <f aca="false">IF(HEX2DEC(D29),HEX2DEC(D29)/HEX2DEC(E29),0)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="21" t="s">
-        <v>48</v>
+      <c r="G29" s="21" t="n">
+        <v>130647</v>
       </c>
       <c r="H29" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D29),HEX2DEC(G29)/HEX2DEC(D29),0.0001)</f>
@@ -1795,7 +1634,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D30" s="24" t="s">
         <v>31</v>
@@ -1807,8 +1646,8 @@
         <f aca="false">IF(HEX2DEC(D30),HEX2DEC(D30)/HEX2DEC(E30),0)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="21" t="s">
-        <v>50</v>
+      <c r="G30" s="21" t="n">
+        <v>581771</v>
       </c>
       <c r="H30" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D30),HEX2DEC(G30)/HEX2DEC(D30),0.0001)</f>
@@ -1820,7 +1659,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D31" s="24" t="s">
         <v>31</v>
@@ -1832,8 +1671,8 @@
         <f aca="false">IF(HEX2DEC(D31),HEX2DEC(D31)/HEX2DEC(E31),0)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="21" t="s">
-        <v>52</v>
+      <c r="G31" s="21" t="n">
+        <v>4240749</v>
       </c>
       <c r="H31" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D31),HEX2DEC(G31)/HEX2DEC(D31),0.0001)</f>
@@ -1845,7 +1684,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D32" s="24" t="s">
         <v>31</v>
@@ -1857,8 +1696,8 @@
         <f aca="false">IF(HEX2DEC(D32),HEX2DEC(D32)/HEX2DEC(E32),0)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="21" t="s">
-        <v>54</v>
+      <c r="G32" s="21" t="n">
+        <v>545430</v>
       </c>
       <c r="H32" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D32),HEX2DEC(G32)/HEX2DEC(D32),0.0001)</f>
@@ -1870,7 +1709,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D33" s="24" t="s">
         <v>31</v>
@@ -1882,8 +1721,8 @@
         <f aca="false">IF(HEX2DEC(D33),HEX2DEC(D33)/HEX2DEC(E33),0)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="21" t="s">
-        <v>56</v>
+      <c r="G33" s="21" t="n">
+        <v>676520</v>
       </c>
       <c r="H33" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D33),HEX2DEC(G33)/HEX2DEC(D33),0.0001)</f>
@@ -1895,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D34" s="24" t="s">
         <v>31</v>
@@ -1907,8 +1746,8 @@
         <f aca="false">IF(HEX2DEC(D34),HEX2DEC(D34)/HEX2DEC(E34),0)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="21" t="s">
-        <v>58</v>
+      <c r="G34" s="21" t="n">
+        <v>6038605</v>
       </c>
       <c r="H34" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D34),HEX2DEC(G34)/HEX2DEC(D34),0.0001)</f>
@@ -1920,7 +1759,7 @@
         <v>15</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D35" s="24" t="s">
         <v>31</v>
@@ -1932,8 +1771,8 @@
         <f aca="false">IF(HEX2DEC(D35),HEX2DEC(D35)/HEX2DEC(E35),0)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="21" t="s">
-        <v>60</v>
+      <c r="G35" s="21" t="n">
+        <v>3906531</v>
       </c>
       <c r="H35" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D35),HEX2DEC(G35)/HEX2DEC(D35),0.0001)</f>
@@ -1945,7 +1784,7 @@
         <v>16</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D36" s="24" t="s">
         <v>31</v>
@@ -1957,8 +1796,8 @@
         <f aca="false">IF(HEX2DEC(D36),HEX2DEC(D36)/HEX2DEC(E36),0)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="21" t="s">
-        <v>62</v>
+      <c r="G36" s="21" t="n">
+        <v>16232737</v>
       </c>
       <c r="H36" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D36),HEX2DEC(G36)/HEX2DEC(D36),0.0001)</f>
@@ -1970,7 +1809,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D37" s="24" t="s">
         <v>31</v>
@@ -1982,8 +1821,8 @@
         <f aca="false">IF(HEX2DEC(D37),HEX2DEC(D37)/HEX2DEC(E37),0)</f>
         <v>0</v>
       </c>
-      <c r="G37" s="21" t="s">
-        <v>64</v>
+      <c r="G37" s="21" t="n">
+        <v>2958023</v>
       </c>
       <c r="H37" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D37),HEX2DEC(G37)/HEX2DEC(D37),0.0001)</f>
@@ -1995,7 +1834,7 @@
         <v>18</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D38" s="24" t="s">
         <v>31</v>
@@ -2007,8 +1846,8 @@
         <f aca="false">IF(HEX2DEC(D38),HEX2DEC(D38)/HEX2DEC(E38),0)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="21" t="s">
-        <v>66</v>
+      <c r="G38" s="21" t="n">
+        <v>11084756</v>
       </c>
       <c r="H38" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D38),HEX2DEC(G38)/HEX2DEC(D38),0.0001)</f>
@@ -2020,7 +1859,7 @@
         <v>19</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D39" s="24" t="s">
         <v>31</v>
@@ -2032,8 +1871,8 @@
         <f aca="false">IF(HEX2DEC(D39),HEX2DEC(D39)/HEX2DEC(E39),0)</f>
         <v>0</v>
       </c>
-      <c r="G39" s="21" t="s">
-        <v>68</v>
+      <c r="G39" s="21" t="n">
+        <v>3395161</v>
       </c>
       <c r="H39" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D39),HEX2DEC(G39)/HEX2DEC(D39),0.0001)</f>
@@ -2045,7 +1884,7 @@
         <v>20</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D40" s="24" t="s">
         <v>31</v>
@@ -2057,8 +1896,8 @@
         <f aca="false">IF(HEX2DEC(D40),HEX2DEC(D40)/HEX2DEC(E40),0)</f>
         <v>0</v>
       </c>
-      <c r="G40" s="21" t="s">
-        <v>70</v>
+      <c r="G40" s="21" t="n">
+        <v>3942826</v>
       </c>
       <c r="H40" s="25" t="n">
         <f aca="false">IF(HEX2DEC(D40),HEX2DEC(G40)/HEX2DEC(D40),0.0001)</f>
@@ -2067,7 +1906,7 @@
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2075,12 +1914,12 @@
     </row>
     <row r="44" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="26" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F44" s="26"/>
       <c r="G44" s="10"/>
@@ -2088,7 +1927,7 @@
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="27" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C45" s="27"/>
       <c r="D45" s="27"/>
@@ -2101,7 +1940,7 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="27" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -2112,7 +1951,7 @@
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="27" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -2123,7 +1962,7 @@
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="27" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -2134,7 +1973,7 @@
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="27" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C49" s="27"/>
       <c r="D49" s="27"/>
@@ -2145,7 +1984,7 @@
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
@@ -2157,7 +1996,7 @@
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="29" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -2169,7 +2008,7 @@
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="29" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
@@ -2181,7 +2020,7 @@
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="10"/>
@@ -2193,7 +2032,7 @@
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -2205,7 +2044,7 @@
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="10"/>
@@ -2283,10 +2122,10 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="30" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="9.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="14.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="30" width="22.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="22.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2303,17 +2142,17 @@
         <v>22</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="18" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2"/>
     </row>
@@ -2339,15 +2178,15 @@
       <c r="B4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>88</v>
+      <c r="C4" s="21" t="n">
+        <v>343640</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>1051297</v>
       </c>
       <c r="E4" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C4),HEX2DEC(C4)/HEX2DEC(D4),0)</f>
-        <v>0.326860619759471</v>
+        <v>0.199990005643013</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2355,17 +2194,17 @@
         <v>2</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>89</v>
+        <v>32</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>1599254</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>4888318</v>
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C5),HEX2DEC(C5)/HEX2DEC(D5),0)</f>
-        <v>0.327144629709051</v>
+        <v>0.297775093182173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2373,17 +2212,17 @@
         <v>3</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>90</v>
+        <v>33</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>4130786</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>12625378</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C6),HEX2DEC(C6)/HEX2DEC(D6),0)</f>
-        <v>0.327185569769546</v>
+        <v>0.221622849201241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2391,17 +2230,17 @@
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>91</v>
+        <v>34</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>2583293</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>7915229</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C7),HEX2DEC(C7)/HEX2DEC(D7),0)</f>
-        <v>0.326597354228554</v>
+        <v>0.30980801566488</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2409,17 +2248,17 @@
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>92</v>
+        <v>35</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>46601</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>144543</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C8),HEX2DEC(C8)/HEX2DEC(D8),0)</f>
-        <v>0.322621375879225</v>
+        <v>0.216987303257704</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2427,17 +2266,17 @@
         <v>6</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>93</v>
+        <v>36</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>1969534</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>6021174</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C9),HEX2DEC(C9)/HEX2DEC(D9),0)</f>
-        <v>0.327167333279242</v>
+        <v>0.264346425587692</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2445,17 +2284,17 @@
         <v>7</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>94</v>
+        <v>37</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>1041006</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>3182355</v>
       </c>
       <c r="E10" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C10),HEX2DEC(C10)/HEX2DEC(D10),0)</f>
-        <v>0.327096173151577</v>
+        <v>0.328304646895993</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2463,17 +2302,17 @@
         <v>8</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>95</v>
+        <v>38</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>2190475</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>6720475</v>
       </c>
       <c r="E11" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C11),HEX2DEC(C11)/HEX2DEC(D11),0)</f>
-        <v>0.326216370878873</v>
+        <v>0.325461662969809</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2481,17 +2320,17 @@
         <v>9</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>96</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>130647</v>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>401411</v>
       </c>
       <c r="E12" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C12),HEX2DEC(C12)/HEX2DEC(D12),0)</f>
-        <v>0.325511773606613</v>
+        <v>0.296894515246196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2499,17 +2338,17 @@
         <v>10</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>97</v>
+        <v>40</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>581771</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>1798925</v>
       </c>
       <c r="E13" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C13),HEX2DEC(C13)/HEX2DEC(D13),0)</f>
-        <v>0.324415704202535</v>
+        <v>0.233333067929622</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2517,17 +2356,17 @@
         <v>11</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>98</v>
+        <v>41</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>4240749</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>12960010</v>
       </c>
       <c r="E14" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C14),HEX2DEC(C14)/HEX2DEC(D14),0)</f>
-        <v>0.327218737704539</v>
+        <v>0.222788651376595</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2535,17 +2374,17 @@
         <v>12</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>99</v>
+        <v>42</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>545430</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>1668123</v>
       </c>
       <c r="E15" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C15),HEX2DEC(C15)/HEX2DEC(D15),0)</f>
-        <v>0.326971885128514</v>
+        <v>0.235224024978648</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2553,17 +2392,17 @@
         <v>13</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>100</v>
+        <v>43</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>676520</v>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>2069036</v>
       </c>
       <c r="E16" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C16),HEX2DEC(C16)/HEX2DEC(D16),0)</f>
-        <v>0.326972398292642</v>
+        <v>0.19938745135071</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2571,17 +2410,17 @@
         <v>14</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>101</v>
+        <v>44</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>6038605</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <v>18453597</v>
       </c>
       <c r="E17" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C17),HEX2DEC(C17)/HEX2DEC(D17),0)</f>
-        <v>0.327230716870441</v>
+        <v>0.247782334491855</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2589,17 +2428,17 @@
         <v>15</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>102</v>
+        <v>45</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>3906531</v>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>11938942</v>
       </c>
       <c r="E18" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C18),HEX2DEC(C18)/HEX2DEC(D18),0)</f>
-        <v>0.3272180495704</v>
+        <v>0.202775407466757</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2607,17 +2446,17 @@
         <v>16</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>103</v>
+        <v>46</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>16232737</v>
+      </c>
+      <c r="D19" s="21" t="n">
+        <v>49602569</v>
       </c>
       <c r="E19" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C19),HEX2DEC(C19)/HEX2DEC(D19),0)</f>
-        <v>0.32725885657884</v>
+        <v>0.301698738006503</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2625,17 +2464,17 @@
         <v>17</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>104</v>
+        <v>47</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>2958023</v>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>9041960</v>
       </c>
       <c r="E20" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C20),HEX2DEC(C20)/HEX2DEC(D20),0)</f>
-        <v>0.32714194745148</v>
+        <v>0.286599707964079</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2643,17 +2482,17 @@
         <v>18</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>105</v>
+        <v>48</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>11084756</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>33873009</v>
       </c>
       <c r="E21" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C21),HEX2DEC(C21)/HEX2DEC(D21),0)</f>
-        <v>0.327254086613709</v>
+        <v>0.330544813392459</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2661,17 +2500,17 @@
         <v>19</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>106</v>
+        <v>49</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>3395161</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>10376199</v>
       </c>
       <c r="E22" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C22),HEX2DEC(C22)/HEX2DEC(D22),0)</f>
-        <v>0.327213312588217</v>
+        <v>0.1988056115474</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,17 +2518,17 @@
         <v>20</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>107</v>
+        <v>50</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>3942826</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>12050280</v>
       </c>
       <c r="E23" s="22" t="n">
         <f aca="false">IF(HEX2DEC(C23),HEX2DEC(C23)/HEX2DEC(D23),0)</f>
-        <v>0.327197030872256</v>
+        <v>0.198602837709332</v>
       </c>
     </row>
   </sheetData>
